--- a/artfynd/A 48925-2025 artfynd.xlsx
+++ b/artfynd/A 48925-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>128340091</v>
       </c>
       <c r="B3" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>128340089</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>128340094</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>128340095</v>
       </c>
       <c r="B6" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>128340090</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128340092</v>
       </c>
       <c r="B8" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128340088</v>
       </c>
       <c r="B9" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>128340096</v>
       </c>
       <c r="B10" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>128340086</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 48925-2025 artfynd.xlsx
+++ b/artfynd/A 48925-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79749981</v>
+        <v>128340092</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Romberg, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521976.8656812692</v>
+        <v>521849</v>
       </c>
       <c r="R2" t="n">
-        <v>6854113.051116656</v>
+        <v>6854280</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-10-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-10-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128340091</v>
+        <v>128340094</v>
       </c>
       <c r="B3" t="n">
-        <v>80229</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521858</v>
+        <v>521852</v>
       </c>
       <c r="R3" t="n">
-        <v>6854291</v>
+        <v>6854269</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,52 +887,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128340089</v>
+        <v>79749981</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Romberg, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521938</v>
+        <v>521977</v>
       </c>
       <c r="R4" t="n">
-        <v>6854266</v>
+        <v>6854113</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,17 +952,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2018-10-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2018-10-22</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128340094</v>
+        <v>128340091</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1043,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521852</v>
+        <v>521858</v>
       </c>
       <c r="R5" t="n">
-        <v>6854269</v>
+        <v>6854291</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1098,7 @@
         <v>128340095</v>
       </c>
       <c r="B6" t="n">
-        <v>80229</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,37 +1201,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128340090</v>
+        <v>128340096</v>
       </c>
       <c r="B7" t="n">
-        <v>98636</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1255,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521862</v>
+        <v>521880</v>
       </c>
       <c r="R7" t="n">
-        <v>6854301</v>
+        <v>6854178</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,37 +1307,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128340092</v>
+        <v>128340086</v>
       </c>
       <c r="B8" t="n">
-        <v>80230</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1361,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521849</v>
+        <v>522003</v>
       </c>
       <c r="R8" t="n">
-        <v>6854280</v>
+        <v>6854170</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1416,7 @@
         <v>128340088</v>
       </c>
       <c r="B9" t="n">
-        <v>98636</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,37 +1519,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128340096</v>
+        <v>128340089</v>
       </c>
       <c r="B10" t="n">
-        <v>80229</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1573,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521880</v>
+        <v>521938</v>
       </c>
       <c r="R10" t="n">
-        <v>6854178</v>
+        <v>6854266</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128340086</v>
+        <v>128340090</v>
       </c>
       <c r="B11" t="n">
-        <v>98636</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1670,7 +1655,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1679,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>522003</v>
+        <v>521862</v>
       </c>
       <c r="R11" t="n">
-        <v>6854170</v>
+        <v>6854301</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 48925-2025 artfynd.xlsx
+++ b/artfynd/A 48925-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340092</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340094</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79749981</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340091</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340095</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340096</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340086</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1516,6 +1556,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340088</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1622,6 +1667,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340089</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1728,8 +1778,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128340090</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>